--- a/output_files/payout_summary.xlsx
+++ b/output_files/payout_summary.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="56">
   <si>
     <t>MID_WID</t>
   </si>
@@ -82,18 +82,21 @@
     <t>1139089</t>
   </si>
   <si>
+    <t>1181484_925160</t>
+  </si>
+  <si>
     <t>1182161</t>
   </si>
   <si>
-    <t>1183547</t>
-  </si>
-  <si>
     <t>1190435</t>
   </si>
   <si>
     <t>1220362</t>
   </si>
   <si>
+    <t>1233229</t>
+  </si>
+  <si>
     <t>1327789</t>
   </si>
   <si>
@@ -109,9 +112,15 @@
     <t>1530557_950125</t>
   </si>
   <si>
+    <t>1530557_950156</t>
+  </si>
+  <si>
     <t>1530559_950162</t>
   </si>
   <si>
+    <t>1530591</t>
+  </si>
+  <si>
     <t>279075_910640</t>
   </si>
   <si>
@@ -127,18 +136,21 @@
     <t>Euronet</t>
   </si>
   <si>
+    <t>Wow Momo</t>
+  </si>
+  <si>
     <t>Euronet Services</t>
   </si>
   <si>
-    <t>Gvs 3rd Party Offers</t>
-  </si>
-  <si>
     <t>Unipin (india) Private Limited</t>
   </si>
   <si>
     <t>PINE LABS Limited</t>
   </si>
   <si>
+    <t>Grapefruit Payment Solutions Private Limited</t>
+  </si>
+  <si>
     <t>Kochi Metro Rail Limited</t>
   </si>
   <si>
@@ -155,6 +167,9 @@
   </si>
   <si>
     <t>Mumbai Metro</t>
+  </si>
+  <si>
+    <t>Rooter Sports Technologies</t>
   </si>
   <si>
     <t>E Xpress Interactive Software PVT LTD</t>
@@ -498,7 +513,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:U16"/>
+  <dimension ref="A1:U19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:21">
@@ -571,19 +586,19 @@
         <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C2">
         <v>1139089</v>
       </c>
       <c r="D2">
-        <v>11931191</v>
+        <v>9808654</v>
       </c>
       <c r="E2">
-        <v>505838.25</v>
+        <v>415847.52</v>
       </c>
       <c r="F2">
-        <v>91078.42999999999</v>
+        <v>74870.63</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -598,16 +613,16 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>11334274.32</v>
+        <v>9317935.85</v>
       </c>
       <c r="L2">
-        <v>1.6</v>
+        <v>0.97</v>
       </c>
       <c r="M2">
-        <v>11131941.77</v>
+        <v>9147611.029999999</v>
       </c>
       <c r="N2">
-        <v>202334.77</v>
+        <v>170326.42</v>
       </c>
       <c r="O2">
         <v>0</v>
@@ -628,7 +643,7 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>11334275.92</v>
+        <v>9317936.82</v>
       </c>
     </row>
     <row r="3" spans="1:21">
@@ -636,19 +651,19 @@
         <v>22</v>
       </c>
       <c r="B3" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C3">
-        <v>1182161</v>
+        <v>1181484</v>
       </c>
       <c r="D3">
-        <v>1531161</v>
+        <v>250</v>
       </c>
       <c r="E3">
-        <v>61633.33</v>
+        <v>50</v>
       </c>
       <c r="F3">
-        <v>11093.82</v>
+        <v>9</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -663,16 +678,16 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>1458433.85</v>
+        <v>191</v>
       </c>
       <c r="L3">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
       <c r="M3">
-        <v>1424074.46</v>
+        <v>161.97</v>
       </c>
       <c r="N3">
-        <v>34359.19</v>
+        <v>29.03</v>
       </c>
       <c r="O3">
         <v>0</v>
@@ -681,7 +696,7 @@
         <v>0</v>
       </c>
       <c r="Q3">
-        <v>4744.04</v>
+        <v>0</v>
       </c>
       <c r="R3">
         <v>0</v>
@@ -693,7 +708,7 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>1458433.65</v>
+        <v>191</v>
       </c>
     </row>
     <row r="4" spans="1:21">
@@ -701,19 +716,19 @@
         <v>23</v>
       </c>
       <c r="B4" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C4">
-        <v>1183547</v>
+        <v>1182161</v>
       </c>
       <c r="D4">
-        <v>30</v>
+        <v>1109205</v>
       </c>
       <c r="E4">
-        <v>30</v>
+        <v>44238.02</v>
       </c>
       <c r="F4">
-        <v>5.4</v>
+        <v>7962.61</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -728,16 +743,16 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>-5.4</v>
+        <v>1057004.37</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>-0.19</v>
       </c>
       <c r="M4">
-        <v>-5.4</v>
+        <v>1030966.03</v>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>26038.15</v>
       </c>
       <c r="O4">
         <v>0</v>
@@ -746,7 +761,7 @@
         <v>0</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>4566.88</v>
       </c>
       <c r="R4">
         <v>0</v>
@@ -758,7 +773,7 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>-5.4</v>
+        <v>1057004.18</v>
       </c>
     </row>
     <row r="5" spans="1:21">
@@ -766,19 +781,19 @@
         <v>24</v>
       </c>
       <c r="B5" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C5">
         <v>1190435</v>
       </c>
       <c r="D5">
-        <v>197639</v>
+        <v>518130</v>
       </c>
       <c r="E5">
-        <v>8316.629999999999</v>
+        <v>32953.1</v>
       </c>
       <c r="F5">
-        <v>1496.93</v>
+        <v>5931.48</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -793,16 +808,16 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>187825.44</v>
+        <v>479245.42</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>-0.27</v>
       </c>
       <c r="M5">
-        <v>185560.71</v>
+        <v>468749.98</v>
       </c>
       <c r="N5">
-        <v>2264.73</v>
+        <v>10495.18</v>
       </c>
       <c r="O5">
         <v>0</v>
@@ -811,7 +826,7 @@
         <v>0</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>373.31</v>
       </c>
       <c r="R5">
         <v>0</v>
@@ -823,7 +838,7 @@
         <v>0</v>
       </c>
       <c r="U5">
-        <v>187825.44</v>
+        <v>479245.15</v>
       </c>
     </row>
     <row r="6" spans="1:21">
@@ -831,19 +846,19 @@
         <v>25</v>
       </c>
       <c r="B6" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C6">
         <v>1220362</v>
       </c>
       <c r="D6">
-        <v>5647290</v>
+        <v>3015496</v>
       </c>
       <c r="E6">
-        <v>394673.82</v>
+        <v>218620.57</v>
       </c>
       <c r="F6">
-        <v>71041.24000000001</v>
+        <v>39351.65</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -858,16 +873,16 @@
         <v>0</v>
       </c>
       <c r="K6">
-        <v>5181574.94</v>
+        <v>2757523.78</v>
       </c>
       <c r="L6">
-        <v>-0.08</v>
+        <v>-0.2</v>
       </c>
       <c r="M6">
-        <v>4922208.41</v>
+        <v>2610732.1</v>
       </c>
       <c r="N6">
-        <v>259366.71</v>
+        <v>146791.62</v>
       </c>
       <c r="O6">
         <v>0</v>
@@ -876,7 +891,7 @@
         <v>0</v>
       </c>
       <c r="Q6">
-        <v>25312.98</v>
+        <v>2746.14</v>
       </c>
       <c r="R6">
         <v>0</v>
@@ -888,7 +903,7 @@
         <v>0</v>
       </c>
       <c r="U6">
-        <v>5181574.86</v>
+        <v>2757523.58</v>
       </c>
     </row>
     <row r="7" spans="1:21">
@@ -896,19 +911,19 @@
         <v>26</v>
       </c>
       <c r="B7" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C7">
-        <v>1327789</v>
+        <v>1233229</v>
       </c>
       <c r="D7">
-        <v>19839</v>
+        <v>1000</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>279.66</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>50.34</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -923,16 +938,16 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>19839</v>
+        <v>670</v>
       </c>
       <c r="L7">
         <v>0</v>
       </c>
       <c r="M7">
-        <v>19839</v>
+        <v>502.5</v>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>167.5</v>
       </c>
       <c r="O7">
         <v>0</v>
@@ -953,7 +968,7 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>19839</v>
+        <v>670</v>
       </c>
     </row>
     <row r="8" spans="1:21">
@@ -961,19 +976,19 @@
         <v>27</v>
       </c>
       <c r="B8" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C8">
-        <v>1337132</v>
+        <v>1327789</v>
       </c>
       <c r="D8">
-        <v>4294496</v>
+        <v>17272</v>
       </c>
       <c r="E8">
-        <v>282727.37</v>
+        <v>0</v>
       </c>
       <c r="F8">
-        <v>50891.14</v>
+        <v>0</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -988,16 +1003,16 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>3960877.49</v>
+        <v>17272</v>
       </c>
       <c r="L8">
-        <v>-1.32</v>
+        <v>0</v>
       </c>
       <c r="M8">
-        <v>3571162.67</v>
+        <v>17272</v>
       </c>
       <c r="N8">
-        <v>389713.83</v>
+        <v>0</v>
       </c>
       <c r="O8">
         <v>0</v>
@@ -1006,7 +1021,7 @@
         <v>0</v>
       </c>
       <c r="Q8">
-        <v>2794.59</v>
+        <v>0</v>
       </c>
       <c r="R8">
         <v>0</v>
@@ -1018,7 +1033,7 @@
         <v>0</v>
       </c>
       <c r="U8">
-        <v>3960876.17</v>
+        <v>17272</v>
       </c>
     </row>
     <row r="9" spans="1:21">
@@ -1026,19 +1041,19 @@
         <v>28</v>
       </c>
       <c r="B9" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C9">
-        <v>1468857</v>
+        <v>1337132</v>
       </c>
       <c r="D9">
-        <v>12449</v>
+        <v>5438952</v>
       </c>
       <c r="E9">
-        <v>814.25</v>
+        <v>263933.97</v>
       </c>
       <c r="F9">
-        <v>146.56</v>
+        <v>47508.64</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -1053,16 +1068,16 @@
         <v>0</v>
       </c>
       <c r="K9">
-        <v>11488.19</v>
+        <v>5127509.39</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>-1.17</v>
       </c>
       <c r="M9">
-        <v>10948</v>
+        <v>4972420.64</v>
       </c>
       <c r="N9">
-        <v>540.1899999999999</v>
+        <v>155088.3</v>
       </c>
       <c r="O9">
         <v>0</v>
@@ -1071,7 +1086,7 @@
         <v>0</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>3921.55</v>
       </c>
       <c r="R9">
         <v>0</v>
@@ -1083,7 +1098,7 @@
         <v>0</v>
       </c>
       <c r="U9">
-        <v>11488.19</v>
+        <v>5127508.22</v>
       </c>
     </row>
     <row r="10" spans="1:21">
@@ -1091,19 +1106,19 @@
         <v>29</v>
       </c>
       <c r="B10" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C10">
-        <v>1470161</v>
+        <v>1468857</v>
       </c>
       <c r="D10">
-        <v>125635</v>
+        <v>5850</v>
       </c>
       <c r="E10">
-        <v>2801.25</v>
+        <v>672.75</v>
       </c>
       <c r="F10">
-        <v>504.2</v>
+        <v>121.1</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -1118,16 +1133,16 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>122329.55</v>
+        <v>5056.15</v>
       </c>
       <c r="L10">
         <v>0</v>
       </c>
       <c r="M10">
-        <v>122329.55</v>
+        <v>4550.54</v>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>505.62</v>
       </c>
       <c r="O10">
         <v>0</v>
@@ -1148,7 +1163,7 @@
         <v>0</v>
       </c>
       <c r="U10">
-        <v>122329.55</v>
+        <v>5056.15</v>
       </c>
     </row>
     <row r="11" spans="1:21">
@@ -1156,19 +1171,19 @@
         <v>30</v>
       </c>
       <c r="B11" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C11">
-        <v>1530557</v>
+        <v>1470161</v>
       </c>
       <c r="D11">
-        <v>9267.5</v>
+        <v>30705</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>657.08</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>118.26</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -1183,13 +1198,13 @@
         <v>0</v>
       </c>
       <c r="K11">
-        <v>9267.5</v>
+        <v>29929.66</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="M11">
-        <v>9267.5</v>
+        <v>29929.65</v>
       </c>
       <c r="N11">
         <v>0</v>
@@ -1213,7 +1228,7 @@
         <v>0</v>
       </c>
       <c r="U11">
-        <v>9267.5</v>
+        <v>29929.65</v>
       </c>
     </row>
     <row r="12" spans="1:21">
@@ -1221,13 +1236,13 @@
         <v>31</v>
       </c>
       <c r="B12" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C12">
-        <v>1530559</v>
+        <v>1530557</v>
       </c>
       <c r="D12">
-        <v>610</v>
+        <v>9103.5</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -1248,13 +1263,13 @@
         <v>0</v>
       </c>
       <c r="K12">
-        <v>610</v>
+        <v>9103.5</v>
       </c>
       <c r="L12">
         <v>0</v>
       </c>
       <c r="M12">
-        <v>610</v>
+        <v>9103.5</v>
       </c>
       <c r="N12">
         <v>0</v>
@@ -1278,7 +1293,7 @@
         <v>0</v>
       </c>
       <c r="U12">
-        <v>610</v>
+        <v>9103.5</v>
       </c>
     </row>
     <row r="13" spans="1:21">
@@ -1286,19 +1301,19 @@
         <v>32</v>
       </c>
       <c r="B13" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C13">
-        <v>279075</v>
+        <v>1530557</v>
       </c>
       <c r="D13">
-        <v>1251000</v>
+        <v>120</v>
       </c>
       <c r="E13">
-        <v>47663.1</v>
+        <v>0</v>
       </c>
       <c r="F13">
-        <v>8579.49</v>
+        <v>0</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -1313,16 +1328,16 @@
         <v>0</v>
       </c>
       <c r="K13">
-        <v>1194757.41</v>
+        <v>120</v>
       </c>
       <c r="L13">
         <v>0</v>
       </c>
       <c r="M13">
-        <v>1178497.39</v>
+        <v>120</v>
       </c>
       <c r="N13">
-        <v>16260.02</v>
+        <v>0</v>
       </c>
       <c r="O13">
         <v>0</v>
@@ -1343,7 +1358,7 @@
         <v>0</v>
       </c>
       <c r="U13">
-        <v>1194757.41</v>
+        <v>120</v>
       </c>
     </row>
     <row r="14" spans="1:21">
@@ -1351,19 +1366,19 @@
         <v>33</v>
       </c>
       <c r="B14" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C14">
-        <v>598341</v>
+        <v>1530559</v>
       </c>
       <c r="D14">
-        <v>2142184</v>
+        <v>26880</v>
       </c>
       <c r="E14">
-        <v>48099.26</v>
+        <v>0</v>
       </c>
       <c r="F14">
-        <v>8656.25</v>
+        <v>0</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -1378,16 +1393,16 @@
         <v>0</v>
       </c>
       <c r="K14">
-        <v>2085428.49</v>
+        <v>26880</v>
       </c>
       <c r="L14">
-        <v>-1.7</v>
+        <v>0</v>
       </c>
       <c r="M14">
-        <v>2079605.89</v>
+        <v>26880</v>
       </c>
       <c r="N14">
-        <v>5820.900000000001</v>
+        <v>0</v>
       </c>
       <c r="O14">
         <v>0</v>
@@ -1396,7 +1411,7 @@
         <v>0</v>
       </c>
       <c r="Q14">
-        <v>2456.18</v>
+        <v>0</v>
       </c>
       <c r="R14">
         <v>0</v>
@@ -1408,7 +1423,7 @@
         <v>0</v>
       </c>
       <c r="U14">
-        <v>2085426.79</v>
+        <v>26880</v>
       </c>
     </row>
     <row r="15" spans="1:21">
@@ -1416,19 +1431,19 @@
         <v>34</v>
       </c>
       <c r="B15" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C15">
-        <v>663553</v>
+        <v>1530591</v>
       </c>
       <c r="D15">
-        <v>3000</v>
+        <v>170</v>
       </c>
       <c r="E15">
-        <v>300</v>
+        <v>8.5</v>
       </c>
       <c r="F15">
-        <v>54</v>
+        <v>1.52</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -1443,16 +1458,16 @@
         <v>0</v>
       </c>
       <c r="K15">
-        <v>2646</v>
+        <v>159.98</v>
       </c>
       <c r="L15">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="M15">
-        <v>2513.7</v>
+        <v>159.96</v>
       </c>
       <c r="N15">
-        <v>132.3</v>
+        <v>0</v>
       </c>
       <c r="O15">
         <v>0</v>
@@ -1461,7 +1476,7 @@
         <v>0</v>
       </c>
       <c r="Q15">
-        <v>24.15</v>
+        <v>0</v>
       </c>
       <c r="R15">
         <v>0</v>
@@ -1473,7 +1488,7 @@
         <v>0</v>
       </c>
       <c r="U15">
-        <v>2646</v>
+        <v>159.96</v>
       </c>
     </row>
     <row r="16" spans="1:21">
@@ -1481,64 +1496,259 @@
         <v>35</v>
       </c>
       <c r="B16" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C16">
+        <v>279075</v>
+      </c>
+      <c r="D16">
+        <v>993000</v>
+      </c>
+      <c r="E16">
+        <v>37833.3</v>
+      </c>
+      <c r="F16">
+        <v>6810.35</v>
+      </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>0</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>948356.35</v>
+      </c>
+      <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16">
+        <v>935849.4400000001</v>
+      </c>
+      <c r="N16">
+        <v>12506.91</v>
+      </c>
+      <c r="O16">
+        <v>0</v>
+      </c>
+      <c r="P16">
+        <v>0</v>
+      </c>
+      <c r="Q16">
+        <v>0</v>
+      </c>
+      <c r="R16">
+        <v>0</v>
+      </c>
+      <c r="S16">
+        <v>0</v>
+      </c>
+      <c r="T16">
+        <v>0</v>
+      </c>
+      <c r="U16">
+        <v>948356.35</v>
+      </c>
+    </row>
+    <row r="17" spans="1:21">
+      <c r="A17" t="s">
+        <v>36</v>
+      </c>
+      <c r="B17" t="s">
+        <v>53</v>
+      </c>
+      <c r="C17">
+        <v>598341</v>
+      </c>
+      <c r="D17">
+        <v>2590301</v>
+      </c>
+      <c r="E17">
+        <v>56844.46</v>
+      </c>
+      <c r="F17">
+        <v>10230.11</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>2523226.43</v>
+      </c>
+      <c r="L17">
+        <v>-2.78</v>
+      </c>
+      <c r="M17">
+        <v>2515116</v>
+      </c>
+      <c r="N17">
+        <v>8107.650000000001</v>
+      </c>
+      <c r="O17">
+        <v>0</v>
+      </c>
+      <c r="P17">
+        <v>0</v>
+      </c>
+      <c r="Q17">
+        <v>2730.48</v>
+      </c>
+      <c r="R17">
+        <v>0</v>
+      </c>
+      <c r="S17">
+        <v>0</v>
+      </c>
+      <c r="T17">
+        <v>0</v>
+      </c>
+      <c r="U17">
+        <v>2523223.65</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21">
+      <c r="A18" t="s">
+        <v>37</v>
+      </c>
+      <c r="B18" t="s">
+        <v>54</v>
+      </c>
+      <c r="C18">
+        <v>663553</v>
+      </c>
+      <c r="D18">
+        <v>3867</v>
+      </c>
+      <c r="E18">
+        <v>386.7</v>
+      </c>
+      <c r="F18">
+        <v>69.61</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <v>3410.69</v>
+      </c>
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18">
+        <v>3240.46</v>
+      </c>
+      <c r="N18">
+        <v>170.23</v>
+      </c>
+      <c r="O18">
+        <v>0</v>
+      </c>
+      <c r="P18">
+        <v>0</v>
+      </c>
+      <c r="Q18">
+        <v>0</v>
+      </c>
+      <c r="R18">
+        <v>0</v>
+      </c>
+      <c r="S18">
+        <v>0</v>
+      </c>
+      <c r="T18">
+        <v>0</v>
+      </c>
+      <c r="U18">
+        <v>3410.69</v>
+      </c>
+    </row>
+    <row r="19" spans="1:21">
+      <c r="A19" t="s">
+        <v>38</v>
+      </c>
+      <c r="B19" t="s">
+        <v>55</v>
+      </c>
+      <c r="C19">
         <v>861793</v>
       </c>
-      <c r="D16">
-        <v>625236</v>
-      </c>
-      <c r="E16">
-        <v>52286.37</v>
-      </c>
-      <c r="F16">
-        <v>9411.4</v>
-      </c>
-      <c r="G16">
-        <v>0</v>
-      </c>
-      <c r="H16">
-        <v>0</v>
-      </c>
-      <c r="I16">
-        <v>0</v>
-      </c>
-      <c r="J16">
-        <v>0</v>
-      </c>
-      <c r="K16">
-        <v>563538.23</v>
-      </c>
-      <c r="L16">
-        <v>-0.29</v>
-      </c>
-      <c r="M16">
-        <v>531127.7</v>
-      </c>
-      <c r="N16">
-        <v>32410.24</v>
-      </c>
-      <c r="O16">
-        <v>0</v>
-      </c>
-      <c r="P16">
-        <v>0</v>
-      </c>
-      <c r="Q16">
-        <v>552.23</v>
-      </c>
-      <c r="R16">
-        <v>0</v>
-      </c>
-      <c r="S16">
-        <v>0</v>
-      </c>
-      <c r="T16">
-        <v>0</v>
-      </c>
-      <c r="U16">
-        <v>563537.9399999999</v>
+      <c r="D19">
+        <v>937447</v>
+      </c>
+      <c r="E19">
+        <v>74572.89</v>
+      </c>
+      <c r="F19">
+        <v>13423.09</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <v>849451.02</v>
+      </c>
+      <c r="L19">
+        <v>-0.2</v>
+      </c>
+      <c r="M19">
+        <v>803489.53</v>
+      </c>
+      <c r="N19">
+        <v>45961.46</v>
+      </c>
+      <c r="O19">
+        <v>0</v>
+      </c>
+      <c r="P19">
+        <v>0</v>
+      </c>
+      <c r="Q19">
+        <v>1040.89</v>
+      </c>
+      <c r="R19">
+        <v>0</v>
+      </c>
+      <c r="S19">
+        <v>0</v>
+      </c>
+      <c r="T19">
+        <v>0</v>
+      </c>
+      <c r="U19">
+        <v>849450.8199999999</v>
       </c>
     </row>
   </sheetData>
